--- a/ploy/resources/sample/AirstrikeRobot‌.xlsx
+++ b/ploy/resources/sample/AirstrikeRobot‌.xlsx
@@ -4,10 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
-    <sheet name="AirstrikeRobot" sheetId="1" r:id="rId1"/>
+    <sheet name="AirstrikeRobot‌" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>

--- a/ploy/resources/sample/AirstrikeRobot‌.xlsx
+++ b/ploy/resources/sample/AirstrikeRobot‌.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="AirstrikeRobot‌" sheetId="1" r:id="rId1"/>
@@ -103,7 +103,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
   <si>
     <t>游戏ID</t>
   </si>
@@ -123,6 +123,9 @@
     <t>机器人下注金额</t>
   </si>
   <si>
+    <t>第二轮下注人数万分比</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -147,6 +150,9 @@
     <t>stake</t>
   </si>
   <si>
+    <t>PeopleNum</t>
+  </si>
+  <si>
     <t>空袭</t>
   </si>
   <si>
@@ -160,6 +166,9 @@
   </si>
   <si>
     <t>1000_10000_5000|10001_50000_3000|50001_200000_1500|200001_500000_400|500001_1000000_100</t>
+  </si>
+  <si>
+    <t>1000_3000</t>
   </si>
 </sst>
 </file>
@@ -880,10 +889,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1240,7 +1249,7 @@
     <col min="4" max="4" width="17.75" customWidth="1"/>
     <col min="5" max="5" width="21.1166666666667" customWidth="1"/>
     <col min="6" max="6" width="15.825" style="3" customWidth="1"/>
-    <col min="7" max="7" width="16.375" style="4" customWidth="1"/>
+    <col min="7" max="7" width="21.25" style="4" customWidth="1"/>
     <col min="8" max="10" width="21.25" customWidth="1"/>
     <col min="11" max="11" width="17.5" customWidth="1"/>
     <col min="12" max="12" width="13.625" customWidth="1"/>
@@ -1266,80 +1275,89 @@
       <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2" s="2" customFormat="1" ht="16.5" spans="1:15">
       <c r="A2" s="9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="11"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
     </row>
     <row r="3" s="2" customFormat="1" ht="16.5" spans="1:15">
       <c r="A3" s="9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="11" t="s">
         <v>12</v>
       </c>
+      <c r="E3" s="12" t="s">
+        <v>13</v>
+      </c>
       <c r="F3" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="11"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
+        <v>14</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
     </row>
     <row r="4" s="2" customFormat="1" ht="16.5" spans="1:15">
       <c r="A4" s="9"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
-      <c r="E4" s="11"/>
+      <c r="E4" s="12"/>
       <c r="F4" s="13"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
     </row>
     <row r="5" ht="16.5" spans="1:15">
       <c r="A5" s="9">
         <v>400400</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" s="9"/>
+        <v>20</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="6" ht="16.5" spans="1:15">
       <c r="A6" s="9"/>

--- a/ploy/resources/sample/AirstrikeRobot‌.xlsx
+++ b/ploy/resources/sample/AirstrikeRobot‌.xlsx
@@ -103,7 +103,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
   <si>
     <t>游戏ID</t>
   </si>
@@ -123,6 +123,9 @@
     <t>机器人下注金额</t>
   </si>
   <si>
+    <t>第二轮下注人数万分比</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -147,6 +150,9 @@
     <t>stake</t>
   </si>
   <si>
+    <t>PeopleNum</t>
+  </si>
+  <si>
     <t>空袭</t>
   </si>
   <si>
@@ -160,6 +166,9 @@
   </si>
   <si>
     <t>1000_10000_5000|10001_50000_3000|50001_200000_1500|200001_500000_400|500001_1000000_100</t>
+  </si>
+  <si>
+    <t>1000_3000</t>
   </si>
 </sst>
 </file>
@@ -880,10 +889,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1240,7 +1249,7 @@
     <col min="4" max="4" width="17.75" customWidth="1"/>
     <col min="5" max="5" width="21.1166666666667" customWidth="1"/>
     <col min="6" max="6" width="15.825" style="3" customWidth="1"/>
-    <col min="7" max="7" width="16.375" style="4" customWidth="1"/>
+    <col min="7" max="7" width="21.25" style="4" customWidth="1"/>
     <col min="8" max="10" width="21.25" customWidth="1"/>
     <col min="11" max="11" width="17.5" customWidth="1"/>
     <col min="12" max="12" width="13.625" customWidth="1"/>
@@ -1266,80 +1275,89 @@
       <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2" s="2" customFormat="1" ht="16.5" spans="1:15">
       <c r="A2" s="9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="11"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
     </row>
     <row r="3" s="2" customFormat="1" ht="16.5" spans="1:15">
       <c r="A3" s="9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="11" t="s">
         <v>12</v>
       </c>
+      <c r="E3" s="12" t="s">
+        <v>13</v>
+      </c>
       <c r="F3" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="11"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
+        <v>14</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
     </row>
     <row r="4" s="2" customFormat="1" ht="16.5" spans="1:15">
       <c r="A4" s="9"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
-      <c r="E4" s="11"/>
+      <c r="E4" s="12"/>
       <c r="F4" s="13"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
     </row>
     <row r="5" ht="16.5" spans="1:15">
       <c r="A5" s="9">
         <v>400400</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" s="9"/>
+        <v>20</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="6" ht="16.5" spans="1:15">
       <c r="A6" s="9"/>

--- a/ploy/resources/sample/AirstrikeRobot‌.xlsx
+++ b/ploy/resources/sample/AirstrikeRobot‌.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="AirstrikeRobot‌" sheetId="1" r:id="rId1"/>
